--- a/output/pdf_financials_xlsx/RCK.xlsx
+++ b/output/pdf_financials_xlsx/RCK.xlsx
@@ -6149,52 +6149,52 @@
         <v>1.680166</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.162092</v>
+        <v>1.750263</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.551302</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.551302</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.601302</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.627296</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.695621</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.29821</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.174111</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>6.725295</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>6.79438</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>8.12772</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>14.220963</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>19.917453</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>22.349727</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>25.470439</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>28.33423</v>
       </c>
     </row>
     <row r="93">
@@ -10776,7 +10776,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -13142,7 +13146,11 @@
           <t>Reserves 8 25,470,439</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -15042,7 +15050,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -17126,7 +17138,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -18048,7 +18064,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -19002,7 +19022,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -19844,7 +19868,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -21000,7 +21028,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -24010,7 +24042,11 @@
           <t>Reserves 8 2,551,302 2,161,757</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -62091,10 +62127,10 @@
         </is>
       </c>
       <c r="L508" s="5" t="n">
-        <v>0.163217</v>
+        <v>-0.163217</v>
       </c>
       <c r="M508" s="5" t="n">
-        <v>0.278231</v>
+        <v>-0.278231</v>
       </c>
       <c r="N508" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RCK.xlsx
+++ b/output/pdf_financials_xlsx/RCK.xlsx
@@ -979,16 +979,16 @@
         <v>5.682383</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>6.57225</v>
+        <v>61.753158</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>3.046735</v>
+        <v>29.089588</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>1.770653</v>
+        <v>15.440982</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>2.414734</v>
+        <v>11.922369</v>
       </c>
     </row>
     <row r="11">
@@ -1040,16 +1040,16 @@
         <v>-5.682383</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-6.57225</v>
+        <v>-61.753158</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-3.046735</v>
+        <v>-29.089588</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-1.770653</v>
+        <v>-15.440982</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-2.414734</v>
+        <v>-11.922369</v>
       </c>
     </row>
     <row r="12">
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.015965</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002311</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1071,10 +1071,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.024214</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.00039</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1104,13 +1104,13 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.389136</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.241574</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>-0.06753199999999999</v>
       </c>
     </row>
     <row r="13">
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.987664</v>
+        <v>-3.003629</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.815481</v>
+        <v>-2.817792</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.353481</v>
@@ -2060,10 +2060,10 @@
         <v>-1.936106</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.210349</v>
+        <v>-5.234563</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-5.217936</v>
+        <v>-5.218326</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-1.42927</v>
@@ -2093,13 +2093,13 @@
         <v>-61.74958</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-28.758345</v>
+        <v>-28.369209</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-15.316475</v>
+        <v>-15.074901</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-11.651137</v>
+        <v>-11.583605</v>
       </c>
     </row>
     <row r="28">
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.987664</v>
+        <v>-3.003629</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.815481</v>
+        <v>-2.817792</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.353481</v>
@@ -2182,10 +2182,10 @@
         <v>-1.936106</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.210349</v>
+        <v>-5.234563</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-5.217936</v>
+        <v>-5.218326</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-1.42927</v>
@@ -2215,13 +2215,13 @@
         <v>-61.74958</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-28.279598</v>
+        <v>-27.890462</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-14.891418</v>
+        <v>-14.649844</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-11.213356</v>
+        <v>-11.145824</v>
       </c>
     </row>
     <row r="30">
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.295526</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.097413</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.097413</v>
@@ -2514,10 +2514,10 @@
         <v>0.269885</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.142201</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>3.08665</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>2.897532</v>
@@ -2541,10 +2541,10 @@
         <v>14.710417</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>3.684092</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>2.660049</v>
       </c>
     </row>
     <row r="35">
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.240389</v>
+        <v>0.535915</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.097413</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.097413</v>
@@ -2636,10 +2636,10 @@
         <v>0.269885</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.142201</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>3.08665</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>2.897532</v>
@@ -2663,10 +2663,10 @@
         <v>14.710417</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>3.684092</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>2.660049</v>
       </c>
     </row>
     <row r="37">
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.312078</v>
+        <v>0.016552</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.105734</v>
+        <v>0.008321</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.008321</v>
@@ -3368,10 +3368,10 @@
         <v>0.221822</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.268274</v>
+        <v>0.126073</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.13585</v>
+        <v>0.0492</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.042462</v>
@@ -3395,10 +3395,10 @@
         <v>0.63092</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>4.052688</v>
+        <v>0.368596</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>3.344863</v>
+        <v>0.684814</v>
       </c>
     </row>
     <row r="49">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -24798,7 +24798,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
@@ -44286,7 +44286,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -44370,10 +44370,10 @@
         </is>
       </c>
       <c r="U338" s="5" t="n">
-        <v>-15.440982</v>
+        <v>15.440982</v>
       </c>
       <c r="V338" s="5" t="n">
-        <v>-11.922369</v>
+        <v>11.922369</v>
       </c>
     </row>
     <row r="339">
@@ -44394,7 +44394,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -47538,7 +47538,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -47617,10 +47617,10 @@
         </is>
       </c>
       <c r="T369" s="5" t="n">
-        <v>-29.089588</v>
+        <v>29.089588</v>
       </c>
       <c r="U369" s="5" t="n">
-        <v>-15.440982</v>
+        <v>15.440982</v>
       </c>
       <c r="V369" t="inlineStr">
         <is>
@@ -47646,7 +47646,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -50364,7 +50364,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -50438,10 +50438,10 @@
         </is>
       </c>
       <c r="S396" s="5" t="n">
-        <v>-61.753158</v>
+        <v>61.753158</v>
       </c>
       <c r="T396" s="5" t="n">
-        <v>-29.089588</v>
+        <v>29.089588</v>
       </c>
       <c r="U396" t="inlineStr">
         <is>
@@ -50472,7 +50472,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -73180,7 +73180,7 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E613" s="5" t="n">

--- a/output/pdf_financials_xlsx/RCK.xlsx
+++ b/output/pdf_financials_xlsx/RCK.xlsx
@@ -1354,7 +1354,7 @@
         <v>-15.316475</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-11.651137</v>
+        <v>-11.635148</v>
       </c>
     </row>
     <row r="17">
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.17885</v>
+        <v>-0.17885</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -1415,7 +1415,7 @@
         <v>0.025577</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.015989</v>
       </c>
     </row>
     <row r="18">
@@ -2099,7 +2099,7 @@
         <v>-15.074901</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-11.583605</v>
+        <v>-11.567616</v>
       </c>
     </row>
     <row r="28">
@@ -2221,7 +2221,7 @@
         <v>-14.649844</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-11.145824</v>
+        <v>-11.129835</v>
       </c>
     </row>
     <row r="30">
@@ -2379,7 +2379,7 @@
         <v>-0.1669901201157577</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.1374198248273249</v>
       </c>
     </row>
     <row r="32">
@@ -4559,49 +4559,49 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.028819</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.036308</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.13064</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="O67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>4.069594</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>2.875543</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>1.0909</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>0.697353</v>
       </c>
     </row>
     <row r="68">
@@ -7206,10 +7206,10 @@
         <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.042329</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.033665</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>0</v>
@@ -30598,7 +30598,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -32912,7 +32916,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -37792,7 +37800,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -42628,7 +42640,11 @@
           <t>- future income tax recovery</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E322" s="5" t="n">
         <v>-0.17885</v>
       </c>
@@ -44814,7 +44830,11 @@
           <t>Current income tax recovery (expense) 16</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -73922,7 +73942,11 @@
           <t>Future income tax recovery (Note 7)</t>
         </is>
       </c>
-      <c r="D620" t="inlineStr"/>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E620" s="5" t="n">
         <v>0.17885</v>
       </c>
